--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_937_Indonesia_Central.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_937_Indonesia_Central.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R0a03e83b4b98421f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Ra0e1c3bc4a994d15"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rb87bcc92b4854a8c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Ra5c1e75ee1bc4d1b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rf7d14671bd5340a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R29ac247fc219479f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Re75e60cce5154d7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R4ef3c47563514195"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R5836ce5961444fd3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rac62f08b69b24e70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rd3299e4d2ce141f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rb59587699a2d464d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ937CommercialTable" displayName="EEZ937CommercialTable" ref="A1:O11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O11"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ937CommercialTable" displayName="EEZ937CommercialTable" ref="A1:E11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E11"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ937FunctionalTable" displayName="EEZ937FunctionalTable" ref="A1:O20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O20"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ937FunctionalTable" displayName="EEZ937FunctionalTable" ref="A1:E20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E20"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ937ValidationTable" displayName="EEZ937ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ937ValidationTable" displayName="EEZ937ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -9940,7 +9894,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca0654d759724f7b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R50efaf62fdae4568"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9950,20 +9904,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -9971,606 +9915,212 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>41989.1355729285</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.4334829825294855</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>271.32073352796164</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>41989.1355729285</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>272.2476286866172</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$139,A2,'Species'!$U$2:$U$139))</x:f>
-        <x:v>11431442.590330668</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.4334829825294855</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>271.32073352796164</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>11392523.063851988</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>38919.52647867985</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0034162341616994</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.0034162341616994327</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>173356.0846305842</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>2.913245530653602</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>81.89276423036686</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>173356.0846305842</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>115.7071181103571</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$139,A3,'Species'!$U$2:$U$139))</x:f>
-        <x:v>20058532.959500067</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>2.913245530653602</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>81.89276423036686</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>14196608.966551956</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>5861923.992948111</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.4129101538796447</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.41291015387964464</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>37.4807979793</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.6460345688407942</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>442.6236027801161</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>37.4807979793</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>631.1796947583412</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$139,A4,'Species'!$U$2:$U$139))</x:f>
-        <x:v>23657.118627873624</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.6460345688407942</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>442.6236027801161</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>16589.88583667146</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>7067.232791202165</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.425996469221039</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.425996469221039</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>170527.0035505027</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>2.824217437078592</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>66.71407011963993</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>170527.0035505027</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>181.56756386955848</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$139,A5,'Species'!$U$2:$U$139))</x:f>
-        <x:v>30962172.608640324</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>2.824217437078592</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>66.71407011963993</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>11376550.472160324</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>19585622.13648</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>2.721578274926849</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>1.721578274926849</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>32522.599628005202</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.058396350290808</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>11.439218362475026</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>32522.599628005202</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>11.512029904632389</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$139,A6,'Species'!$U$2:$U$139))</x:f>
-        <x:v>374401.1394939821</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.058396350290808</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>11.439218362475026</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>372033.11886010057</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>2368.020633881504</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0063650801873152</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.006365080187315192</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>544791.0815039099</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.3110427061279575</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>204.66458827162856</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>544791.0815039099</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>211.52701037239953</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$139,A7,'Species'!$U$2:$U$139))</x:f>
-        <x:v>115238028.7480683</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.3110427061279575</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>204.66458827162856</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>111499442.39005296</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>3738586.3580153435</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.033530090176925</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.033530090176925126</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>808276.3326102103</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.6257926454218405</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>422.4668586441917</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>808276.3326102103</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>824.3950263210908</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$139,A8,'Species'!$U$2:$U$139))</x:f>
-        <x:v>666338988.496909</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.6257926454218405</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>422.4668586441917</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>341469963.15428334</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>324869025.3426257</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.9513839001875635</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.9513839001875635</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>339.1715827005</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.9</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>794.3282347242813</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>339.1715827005</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>794.3282347242813</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$139,A9,'Species'!$U$2:$U$139))</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>269413.56455512875</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.9</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>794.3282347242813</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
-        <x:v>269413.56455512875</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>43932.975511280805</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.620311749597156</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>417.1687322374211</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>43932.975511280805</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>738.4339290148384</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$139,A10,'Species'!$U$2:$U$139))</x:f>
-        <x:v>32441599.720107768</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.620311749597156</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>417.1687322374211</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>18327463.69745868</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>14114136.022649087</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.7701085243238637</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.7701085243238637</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>60464.0172851735</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.396105769803435</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>2489.463538298732</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>60464.0172851735</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>2498.0101336715156</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$139,A11,'Species'!$U$2:$U$139))</x:f>
-        <x:v>151039727.90085307</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.396105769803435</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>2489.463538298732</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>150522966.41050372</x:v>
       </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>516761.49034935236</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0034331072704217</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.0034331072704217713</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G11">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O11">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf6eac7bc6984691"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R76b921277ac94af9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10580,20 +10130,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -10601,1092 +10141,383 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>806.5144277817</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.9867633083842255</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>969.981180911535</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>806.5144277817</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1052.8225401665184</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$139,A2,'Species'!$U$2:$U$139))</x:f>
-        <x:v>849116.5685380754</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.9867633083842255</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>969.981180911535</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>782303.8170818842</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>66812.75145619118</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.085405120104633</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.08540512010463301</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Jellyfish</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>9848.021344513598</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.460000000000001</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>288.4031503126612</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>9848.021344513598</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>288.40315031266056</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$139,A3,'Species'!$U$2:$U$139))</x:f>
-        <x:v>2840200.380104045</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.460000000000001</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>288.4031503126612</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>2840200.380104051</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>-6.05359673500061e-9</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>0.9999999999999979</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>-2.1313977624278878e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>32221.745937441603</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.1708466012369625</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>1481.9945319088224</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>32221.745937441603</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1484.75171368758</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$139,A4,'Species'!$U$2:$U$139))</x:f>
-        <x:v>47841292.49862224</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.1708466012369625</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>1481.9945319088224</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>47752451.28784377</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>88841.21077846736</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0018604534088302</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.001860453408830207</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>79865.9531469162</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.7721943830956888</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>591.8264667351787</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>79865.9531469162</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>888.9390672466981</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$139,A5,'Species'!$U$2:$U$139))</x:f>
-        <x:v>70995965.89518818</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.7721943830956888</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>591.8264667351787</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>47266784.86337674</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>23729181.031811446</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.5020265520576437</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.5020265520576437</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>101764.20502699321</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.484876928398668</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>3054.0555236633804</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>101764.20502699321</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>3061.020193151913</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$139,A6,'Species'!$U$2:$U$139))</x:f>
-        <x:v>311502286.52767766</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.484876928398668</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>3054.0555236633804</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>310793532.47390133</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>708754.0537763238</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.002280465903311</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.0022804659033110377</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>28383.6432814383</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.280837276870121</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>190.91378014318659</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>28383.6432814383</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>190.97625053065505</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$139,A7,'Species'!$U$2:$U$139))</x:f>
-        <x:v>5420601.770288705</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.280837276870121</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>190.91378014318659</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>5418828.633095147</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>1773.1371935578063</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0003272178017826</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.0003272178017825633</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>15549.3322298425</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.239986099248384</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1737.7452066954713</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>15549.3322298425</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1737.7593809437024</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$139,A8,'Species'!$U$2:$U$139))</x:f>
-        <x:v>27020997.949819062</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.239986099248384</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1737.7452066954713</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>27020777.549724206</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>220.40009485557675</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0000081566895864</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.00000815668958637448</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>52034.896168501095</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.4269225000294488</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>267.252945248728</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>52034.896168501095</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>268.36939061767424</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$139,A9,'Species'!$U$2:$U$139))</x:f>
-        <x:v>13964573.37559459</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.4269225000294488</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>267.252945248728</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>13906479.25674367</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>58094.11885092035</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0041774857444776</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.004177485744477616</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>47860.4929024317</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.0586008764225325</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>114.44606803209047</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>47860.4929024317</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>125.02423588696541</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$139,A10,'Species'!$U$2:$U$139))</x:f>
-        <x:v>5983721.554300055</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.0586008764225325</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>114.44606803209047</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>5477445.226761081</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>506276.32753897365</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.092429281641278</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.09242928164127796</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>495857.89081077266</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.3054411337334373</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>202.04175567664726</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>495857.89081077266</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>212.2082874100251</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$139,A11,'Species'!$U$2:$U$139))</x:f>
-        <x:v>105225153.80770129</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.3054411337334373</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>202.04175567664726</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>100183998.82552776</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>5041154.982173532</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.050318963519841</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.050318963519841074</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>252250.2510030519</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.4658153199699337</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>292.2909171296375</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>252250.2510030519</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>706.6186697665039</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$139,A12,'Species'!$U$2:$U$139))</x:f>
-        <x:v>178244736.81204325</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.4658153199699337</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>292.2909171296375</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>73730457.2118633</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>104514279.60017996</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>2.4175183981276533</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>1.4175183981276536</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>140298.8923278258</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.420025756460674</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>263.0423988358282</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>140298.8923278258</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>518.9016578407196</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$139,A13,'Species'!$U$2:$U$139))</x:f>
-        <x:v>72801327.82212543</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.420025756460674</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>263.0423988358282</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>36904557.19192087</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>35896770.630204566</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.972692083623295</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.972692083623295</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>32531.087366140604</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>2.0584933059945443</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>11.44177243885471</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>32531.087366140604</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>11.51604880905054</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$139,A14,'Species'!$U$2:$U$139))</x:f>
-        <x:v>374629.5899199626</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>2.0584933059945443</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>11.44177243885471</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>372213.2988318822</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>2416.291088080383</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.0064916839233402</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.006491683923340285</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>121321.18846208311</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>2.6929284689395536</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>49.30925817851469</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>121321.18846208311</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>50.229969399038986</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$139,A15,'Species'!$U$2:$U$139))</x:f>
-        <x:v>6093959.583905476</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>2.6929284689395536</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>49.30925817851469</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>5982257.804401093</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>111701.77950438298</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.018672177488273</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.018672177488272903</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>46957.1133305117</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.221790591081341</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>166.64434899840896</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>46957.1133305117</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>166.99266650105668</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$139,A16,'Species'!$U$2:$U$139))</x:f>
-        <x:v>7841493.566254463</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.221790591081341</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>166.64434899840896</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>7825137.581807633</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>16355.984446830116</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.002090184904206</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.002090184904206097</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>113978.3833285365</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.762081921288695</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>578.2051043752855</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>113978.3833285365</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>598.0483935771878</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$139,A17,'Species'!$U$2:$U$139))</x:f>
-        <x:v>68164589.05215617</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.762081921288695</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>578.2051043752855</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>65902883.02900274</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>2261706.0231534243</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.034318772096178</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.034318772096178035</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>284520.0851442628</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.150778462285111</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>141.50717543567532</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>284520.0851442628</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>278.95519934549395</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$139,A18,'Species'!$U$2:$U$139))</x:f>
-        <x:v>79368357.06921475</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.150778462285111</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>141.50717543567532</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>40261633.60348248</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>39106723.46573227</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.9713148713953248</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.9713148713953248</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>20148.7056362505</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>4.067987630361435</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>1169.4660816425735</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>20148.7056362505</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>1172.3484541114467</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$139,A19,'Species'!$U$2:$U$139))</x:f>
-        <x:v>23621303.905004866</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>4.067987630361435</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>1169.4660816425735</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>23563227.83059551</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>58076.0744093582</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.002464690950955</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.0024646909509549336</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>37.4807979793</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.6460345688407942</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>442.6236027801161</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>37.4807979793</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>631.1796947583412</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$139,A20,'Species'!$U$2:$U$139))</x:f>
-        <x:v>23657.118627873624</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.6460345688407942</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>442.6236027801161</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>16589.88583667146</x:v>
       </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>7067.232791202165</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.425996469221039</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.425996469221039</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G20">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O20">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac9e7185ca3d4d36"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0cdbc1b9e5a04288"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11861,7 +10692,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -11960,7 +10791,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>1028177964.8470862</x:v>
+        <x:v>659443554.7241148</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -11974,7 +10805,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>1028177964.8470862</x:v>
+        <x:v>816001759.7519019</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -11988,7 +10819,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>-1.1920928955078125e-7</x:v>
+        <x:v>-368734410.12297153</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -12002,7 +10833,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>-1.1920928955078125e-7</x:v>
+        <x:v>-212176205.09518445</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -12013,9 +10844,9 @@
         <x:v>EEZ_937</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -12027,47 +10858,19 @@
         <x:v>EEZ_937</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_937</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_937</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf7b54b9a41db4257"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R00b446c41e2a4003"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12114,7 +10917,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
